--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programma" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classifiche" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gironi &amp; Squadre" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impianti" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cerimonie" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Programma" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Classifiche" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gironi &amp; Squadre" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Impianti" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cerimonie" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Dany Basket</t>
+          <t>Basket Marsciano</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>Mens Sana Siena</t>
+          <t>Endas Pistoia</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>Girone B13</t>
+          <t>Girone A13</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Basket Marsciano</t>
+          <t>Dany Basket</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>Endas Pistoia</t>
+          <t>Mens Sana Siena</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>Girone A13</t>
+          <t>Girone B13</t>
         </is>
       </c>
     </row>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers</t>
+          <t>Codigoro Basket</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>TissIttiri</t>
+          <t>Prato Dragons</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>Girone A13</t>
+          <t>Girone B13</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Codigoro Basket</t>
+          <t>Shoemakers</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Prato Dragons</t>
+          <t>TissIttiri</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>Girone B13</t>
+          <t>Girone A13</t>
         </is>
       </c>
     </row>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Gironi &amp; Squadre" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Impianti" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cerimonie" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Mensa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,8 +105,14 @@
       <color rgb="00166534"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -152,6 +159,21 @@
         <fgColor rgb="00EFFAE8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -179,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -267,6 +289,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4209,4 +4243,910 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PROGRAMMA PRANZI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ Schema in revisione (4 turni × 45 min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Turno</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Cat.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Squadra / Voce</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Provenienza</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GIORNO 1 — Venerdì 1 Maggio</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟢 Turno 13:00 · 8 squadre</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Dany Basket</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 10:00</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Prato Dragons</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 10:00</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Shoemakers</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Cintolese 10:00</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Endas Pistoia</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Cintolese 10:00</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Basket Calcinaia</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Salutati 10:00</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Massa e Cozzile</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Salutati 10:00</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Cestistica Pescia</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Geodetica 10:00</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Chiesina Basket</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Geodetica 10:00</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟠 Turno 14:00 · ✈ fuori regione</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Codigoro Basket</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 12:00</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Mens Sana Siena</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 12:00</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Basket Marsciano</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Cintolese 12:00</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>TissIttiri</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Cintolese 12:00</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr"/>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Basket Loano</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Salutati 12:00</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Shoemakers</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Salutati 12:00</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>La T Gema</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Geodetica 12:00</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>San Fr. Ittiri</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Geodetica 12:00</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GIORNO 2 — Sabato 2 Maggio</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟢 Turno 12:00 · 8 squadre</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Codigoro Basket</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 09:00</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Prato Dragons</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 09:00</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Basket Marsciano</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Cintolese 09:00</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr"/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Endas Pistoia</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Cintolese 09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Massa e Cozzile</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Salutati 09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr"/>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Shoemakers</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Salutati 09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr"/>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Cestistica Pescia</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Geodetica 09:00</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>La T Gema</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Geodetica 09:00</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟠 Turno 13:00 · 8 squadre</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr"/>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Basket Calcinaia</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 11:00</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr"/>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Basket Loano</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 11:00</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Dany Basket</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Cintolese 11:00</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr"/>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Mens Sana Siena</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Cintolese 11:00</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr"/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Shoemakers</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Salutati 11:00</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr"/>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>TissIttiri</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Salutati 11:00</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr"/>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Chiesina Basket</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Geodetica 11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr"/>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>San Fr. Ittiri</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Geodetica 11:00</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GIORNO 3 — Domenica 3 Maggio</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟢 Turno 12:00 · finali mattutine U13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr"/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Finale 3°/4°</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Pala 09:00</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr"/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Finale 5°/6°</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Geodetica 09:00</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr"/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Finale 7°/8°</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Cintolese 09:00</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟠 Turno 13:00 · prima delle finalissime</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr"/>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Finale 3°/4°</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Pala 11:00</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr"/>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Finale 5°/6°</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Geodetica 11:00</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr"/>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Finale 7°/8°</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Cintolese 11:00</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr"/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>🏆 Finaliste U13</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>(prima della finale)</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟡 Turno 14:30 · finaliste U14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr"/>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>🏆 Finaliste U14</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>(prima della finale 15:00)</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -3955,7 +3955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4134,6 +4134,33 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>☕</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Caffè Micky</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Cintolese · Monsummano Terme</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Punto di ristoro ufficiale per i pranzi delle squadre che giocano alla Pal. Cintolese.</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>📍 Apri su Maps</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
@@ -4144,6 +4171,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Cestistica Pescia</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Cestistica Pescia</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Cestistica Pescia</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Cestistica Audace Pescia</t>
+          <t>Basket Fucecchio</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Cestistica Audace Pescia</t>
+          <t>Basket Fucecchio</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Pescia</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Cestistica Pescia</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Cestistica Pescia</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,12 +105,6 @@
       <color rgb="00166534"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B45309"/>
-      <sz val="11"/>
-    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -161,17 +155,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -201,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -290,16 +284,13 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -4279,7 +4270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4296,53 +4287,65 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
-        <is>
-          <t>⚠️ Schema in revisione (4 turni × 45 min)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Turno</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Squadra / Voce</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Provenienza</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  GIORNO 1 — Venerdì 1 Maggio</t>
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟢 Turno 13:00 · 8 squadre</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟢 Turno 13:00 · 8 squadre</t>
-        </is>
-      </c>
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Dany Basket</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 10:00</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr"/>
@@ -4353,7 +4356,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Dany Basket</t>
+          <t>Prato Dragons</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -4372,12 +4375,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Prato Dragons</t>
+          <t>Shoemakers</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>🏟 PalaCardelli 10:00</t>
+          <t>Cintolese 10:00</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr"/>
@@ -4391,7 +4394,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers</t>
+          <t>Endas Pistoia</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -4403,19 +4406,19 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Endas Pistoia</t>
+          <t>Basket Calcinaia</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Cintolese 10:00</t>
+          <t>Salutati 10:00</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr"/>
@@ -4429,7 +4432,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Basket Calcinaia</t>
+          <t>Massa e Cozzile</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -4448,12 +4451,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Massa e Cozzile</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Salutati 10:00</t>
+          <t>Geodetica 10:00</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr"/>
@@ -4467,7 +4470,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Fucecchio</t>
+          <t>Chiesina Basket</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -4478,30 +4481,30 @@
       <c r="E13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Chiesina Basket</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 10:00</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr"/>
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟠 Turno 14:00 · ✈ fuori regione</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟠 Turno 14:00 · ✈ fuori regione</t>
-        </is>
-      </c>
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Codigoro Basket</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 12:00</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr"/>
@@ -4512,7 +4515,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Codigoro Basket</t>
+          <t>Mens Sana Siena</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -4531,12 +4534,12 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Mens Sana Siena</t>
+          <t>Basket Marsciano</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>🏟 PalaCardelli 12:00</t>
+          <t>Cintolese 12:00</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr"/>
@@ -4550,7 +4553,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Basket Marsciano</t>
+          <t>TissIttiri</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -4562,19 +4565,19 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>TissIttiri</t>
+          <t>Basket Loano</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Cintolese 12:00</t>
+          <t>Salutati 12:00</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
@@ -4588,7 +4591,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Basket Loano</t>
+          <t>Shoemakers</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -4607,12 +4610,12 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers</t>
+          <t>La T Gema</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Salutati 12:00</t>
+          <t>Geodetica 12:00</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
@@ -4626,7 +4629,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>La T Gema</t>
+          <t>San Fr. Ittiri</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -4636,38 +4639,38 @@
       </c>
       <c r="E22" s="8" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>San Fr. Ittiri</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 12:00</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  GIORNO 2 — Sabato 2 Maggio</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟢 Turno 12:00 · 8 squadre</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟢 Turno 12:00 · 8 squadre</t>
-        </is>
-      </c>
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Codigoro Basket</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 09:00</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr"/>
@@ -4678,7 +4681,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Codigoro Basket</t>
+          <t>Prato Dragons</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -4697,12 +4700,12 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Prato Dragons</t>
+          <t>Basket Marsciano</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>🏟 PalaCardelli 09:00</t>
+          <t>Cintolese 09:00</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
@@ -4716,7 +4719,7 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Basket Marsciano</t>
+          <t>Endas Pistoia</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -4728,19 +4731,19 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr"/>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Endas Pistoia</t>
+          <t>Massa e Cozzile</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Cintolese 09:00</t>
+          <t>Salutati 09:00</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr"/>
@@ -4754,7 +4757,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Massa e Cozzile</t>
+          <t>Shoemakers</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -4773,12 +4776,12 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Salutati 09:00</t>
+          <t>Geodetica 09:00</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr"/>
@@ -4792,7 +4795,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Fucecchio</t>
+          <t>La T Gema</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -4803,30 +4806,30 @@
       <c r="E33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr"/>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟠 Turno 13:00 · 8 squadre</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr"/>
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>La T Gema</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 09:00</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟠 Turno 13:00 · 8 squadre</t>
-        </is>
-      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Basket Calcinaia</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli 11:00</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr"/>
@@ -4837,7 +4840,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Basket Calcinaia</t>
+          <t>Basket Loano</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -4849,19 +4852,19 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr"/>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Basket Loano</t>
+          <t>Dany Basket</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>🏟 PalaCardelli 11:00</t>
+          <t>Cintolese 11:00</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr"/>
@@ -4875,7 +4878,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Dany Basket</t>
+          <t>Mens Sana Siena</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -4894,12 +4897,12 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Mens Sana Siena</t>
+          <t>Shoemakers</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Cintolese 11:00</t>
+          <t>Salutati 11:00</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr"/>
@@ -4913,7 +4916,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers</t>
+          <t>TissIttiri</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -4925,19 +4928,19 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr"/>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>TissIttiri</t>
+          <t>Chiesina Basket</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Salutati 11:00</t>
+          <t>Geodetica 11:00</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr"/>
@@ -4951,7 +4954,7 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Chiesina Basket</t>
+          <t>San Fr. Ittiri</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -4961,38 +4964,38 @@
       </c>
       <c r="E42" s="8" t="inlineStr"/>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr"/>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>San Fr. Ittiri</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 11:00</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  GIORNO 3 — Domenica 3 Maggio</t>
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟢 Turno 12:00 · finali mattutine U13</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
-      <c r="A46" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟢 Turno 12:00 · finali mattutine U13</t>
-        </is>
-      </c>
+      <c r="A46" s="5" t="inlineStr"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Finale 3°/4°</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Pala 09:00</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr"/>
@@ -5003,12 +5006,12 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Finale 3°/4°</t>
+          <t>Finale 5°/6°</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Pala 09:00</t>
+          <t>Geodetica 09:00</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr"/>
@@ -5022,41 +5025,41 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Finale 5°/6°</t>
+          <t>Finale 7°/8°</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Geodetica 09:00</t>
+          <t>Cintolese 09:00</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr"/>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>Finale 7°/8°</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 09:00</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr"/>
+      <c r="A49" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟠 Turno 13:00 · prima delle finalissime</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟠 Turno 13:00 · prima delle finalissime</t>
-        </is>
-      </c>
+      <c r="A50" s="5" t="inlineStr"/>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Finale 3°/4°</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Pala 11:00</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr"/>
@@ -5067,12 +5070,12 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Finale 3°/4°</t>
+          <t>Finale 5°/6°</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Pala 11:00</t>
+          <t>Geodetica 11:00</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr"/>
@@ -5086,94 +5089,74 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Finale 5°/6°</t>
+          <t>Finale 7°/8°</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Geodetica 11:00</t>
+          <t>Cintolese 11:00</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr"/>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>🏆 Finaliste U13</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>(prima della finale)</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🟡 Turno 14:30 · finaliste U14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr"/>
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>Finale 7°/8°</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 11:00</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr"/>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>🏆 Finaliste U13</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>(prima della finale)</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟡 Turno 14:30 · finaliste U14</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr"/>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>🏆 Finaliste U14</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>(prima della finale 15:00)</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr"/>
+      <c r="E55" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A15:E15"/>
+  <mergeCells count="11">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A54:E54"/>
     <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A44:E44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -290,8 +290,8 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4270,7 +4270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4300,17 +4300,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Squadra / Voce</t>
+          <t>Squadra</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Provenienza</t>
+          <t>PAX</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Allergie &amp; intolleranze</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
     <row r="5">
       <c r="A5" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🟢 Turno 13:00 · 8 squadre</t>
+          <t xml:space="preserve">  ☕ Caffè Micky · 12:30 · 24 coperti</t>
         </is>
       </c>
     </row>
@@ -4337,53 +4337,45 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Dany Basket</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>🏟 PalaCardelli 10:00</t>
+          <t>Endas Pistoia</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>24 pax</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Prato Dragons</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>🏟 PalaCardelli 10:00</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr"/>
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 25 coperti · ⚠ allergie</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 10:00</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr"/>
+          <t>Chiesina Basket</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>15 pax</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
@@ -4394,88 +4386,84 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Endas Pistoia</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 10:00</t>
+          <t>Dany Basket</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>10 pax</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Basket Calcinaia</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Salutati 10:00</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr"/>
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ☕ Caffè Micky · 14:00 · 76 coperti · ⚠ allergie</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr"/>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Massa e Cozzile</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Salutati 10:00</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr"/>
+          <t>Mens Sana Siena</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>36 pax</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Fucecchio</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 10:00</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr"/>
+          <t>TissIttiri</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>24 pax</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Chiesina Basket</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 10:00</t>
+          <t>Basket Marsciano</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>16 pax</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr"/>
@@ -4483,7 +4471,7 @@
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🟠 Turno 14:00 · ✈ fuori regione</t>
+          <t xml:space="preserve">  🍽 Pool Bar · 14:00 · 65 coperti · ⚠ allergie</t>
         </is>
       </c>
     </row>
@@ -4499,178 +4487,154 @@
           <t>Codigoro Basket</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>🏟 PalaCardelli 12:00</t>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>35 pax</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Mens Sana Siena</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>🏟 PalaCardelli 12:00</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr"/>
+          <t>Basket Loano</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>18 pax</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Basket Marsciano</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 12:00</t>
+          <t>San Fr. Ittiri</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>12 pax</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>TissIttiri</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 12:00</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Basket Loano</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Salutati 12:00</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr"/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GIORNO 2 — Sabato 2 Maggio</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Shoemakers</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Salutati 12:00</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr"/>
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ☕ Caffè Micky · 12:30 · 16 coperti</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>La T Gema</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 12:00</t>
+          <t>Basket Marsciano</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>16 pax</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr"/>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>San Fr. Ittiri</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 12:00</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  GIORNO 2 — Sabato 2 Maggio</t>
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 24 coperti · ⚠ allergie</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>TissIttiri</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>24 pax</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ☕ Caffè Micky · 13:30 · 4 coperti · ⚠ allergie</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟢 Turno 12:00 · 8 squadre</t>
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Mens Sana Siena</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>4 pax</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr"/>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Codigoro Basket</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>🏟 PalaCardelli 09:00</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr"/>
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🍽 Pool Bar · 13:30 · 80 coperti · ⚠ allergie</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr"/>
@@ -4681,53 +4645,61 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Prato Dragons</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>🏟 PalaCardelli 09:00</t>
+          <t>Codigoro Basket</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>35 pax</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr"/>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Basket Marsciano</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 09:00</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr"/>
+          <t>Basket Loano</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>18 pax</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr"/>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Endas Pistoia</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 09:00</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr"/>
+          <t>Chiesina Basket</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>15 pax</t>
+        </is>
+      </c>
+      <c r="E29" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr"/>
@@ -4738,98 +4710,71 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Massa e Cozzile</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Salutati 09:00</t>
+          <t>San Fr. Ittiri</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>12 pax</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr"/>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Shoemakers</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Salutati 09:00</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr"/>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Fucecchio</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 09:00</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr"/>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GIORNO 3 — Domenica 3 Maggio</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr"/>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>La T Gema</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 09:00</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr"/>
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🍽 Pool Bar · 14:00 · 120 coperti · ⚠ allergie</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟠 Turno 13:00 · 8 squadre</t>
-        </is>
-      </c>
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Codigoro Basket</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>35 pax</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr"/>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Basket Calcinaia</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>🏟 PalaCardelli 11:00</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr"/>
+          <t>TissIttiri</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>24 pax</t>
+        </is>
+      </c>
+      <c r="E35" s="32" t="inlineStr">
+        <is>
+          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr"/>
@@ -4843,12 +4788,16 @@
           <t>Basket Loano</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>🏟 PalaCardelli 11:00</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>18 pax</t>
+        </is>
+      </c>
+      <c r="E36" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr"/>
@@ -4859,304 +4808,73 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Dany Basket</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 11:00</t>
+          <t>Basket Marsciano</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>16 pax</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr"/>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Mens Sana Siena</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 11:00</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr"/>
+          <t>Chiesina Basket</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>15 pax</t>
+        </is>
+      </c>
+      <c r="E38" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr"/>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Salutati 11:00</t>
+          <t>San Fr. Ittiri</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>12 pax</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr"/>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr"/>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>TissIttiri</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Salutati 11:00</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr"/>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Chiesina Basket</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 11:00</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr"/>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>San Fr. Ittiri</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 11:00</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  GIORNO 3 — Domenica 3 Maggio</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟢 Turno 12:00 · finali mattutine U13</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr"/>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>Finale 3°/4°</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Pala 09:00</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr"/>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>Finale 5°/6°</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 09:00</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr"/>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>Finale 7°/8°</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 09:00</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟠 Turno 13:00 · prima delle finalissime</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr"/>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>Finale 3°/4°</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>Pala 11:00</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr"/>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>Finale 5°/6°</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Geodetica 11:00</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr"/>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>Finale 7°/8°</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>Cintolese 11:00</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr"/>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>🏆 Finaliste U13</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>(prima della finale)</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟡 Turno 14:30 · finaliste U14</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr"/>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>🏆 Finaliste U14</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>(prima della finale 15:00)</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A34:E34"/>
+  <mergeCells count="13">
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -4399,7 +4399,7 @@
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ☕ Caffè Micky · 14:00 · 76 coperti · ⚠ allergie</t>
+          <t xml:space="preserve">  ☕ Caffè Micky · 14:00 · 40 coperti · ⚠ allergie</t>
         </is>
       </c>
     </row>
@@ -4412,17 +4412,17 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Mens Sana Siena</t>
+          <t>TissIttiri</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>36 pax</t>
+          <t>24 pax</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
-          <t>⚠ 1 celiaco</t>
+          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
         </is>
       </c>
     </row>
@@ -4435,43 +4435,43 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>TissIttiri</t>
+          <t>Basket Marsciano</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>24 pax</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
-        </is>
-      </c>
+          <t>16 pax</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🍽 Pool Bar · 14:00 · 101 coperti · ⚠ allergie</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>U13</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Basket Marsciano</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>16 pax</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🍽 Pool Bar · 14:00 · 65 coperti · ⚠ allergie</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Mens Sana Siena</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>36 pax</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -4270,7 +4270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4720,148 +4720,8 @@
       </c>
       <c r="E30" s="8" t="inlineStr"/>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  GIORNO 3 — Domenica 3 Maggio</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🍽 Pool Bar · 14:00 · 120 coperti · ⚠ allergie</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr"/>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Codigoro Basket</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>35 pax</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr"/>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>TissIttiri</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>24 pax</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="inlineStr">
-        <is>
-          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr"/>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Basket Loano</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>18 pax</t>
-        </is>
-      </c>
-      <c r="E36" s="32" t="inlineStr">
-        <is>
-          <t>⚠ 1 celiaco</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr"/>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Basket Marsciano</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>16 pax</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr"/>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>Chiesina Basket</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>15 pax</t>
-        </is>
-      </c>
-      <c r="E38" s="32" t="inlineStr">
-        <is>
-          <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr"/>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>San Fr. Ittiri</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>12 pax</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="11">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A24:E24"/>
@@ -4869,10 +4729,8 @@
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A22:E22"/>
   </mergeCells>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -4350,7 +4350,7 @@
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 25 coperti · ⚠ allergie</t>
+          <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 32 coperti · ⚠ allergie</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>10 pax</t>
+          <t>17 pax</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr"/>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -4350,7 +4350,7 @@
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 32 coperti · ⚠ allergie</t>
+          <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 38 coperti · ⚠ allergie</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>17 pax</t>
+          <t>23 pax</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr"/>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -4270,7 +4270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4350,7 +4350,7 @@
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 38 coperti · ⚠ allergie</t>
+          <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 42 coperti · ⚠ allergie</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>23 pax</t>
+          <t>27 pax</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr"/>
@@ -4602,7 +4602,7 @@
     <row r="24">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ☕ Caffè Micky · 13:30 · 4 coperti · ⚠ allergie</t>
+          <t xml:space="preserve">  ☕ Caffè Micky · 13:30 · 35 coperti · ⚠ allergie</t>
         </is>
       </c>
     </row>
@@ -4630,53 +4630,49 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Dany Basket</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>31 pax</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  🍽 Pool Bar · 13:30 · 80 coperti · ⚠ allergie</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Codigoro Basket</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>35 pax</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr"/>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Basket Loano</t>
+          <t>Codigoro Basket</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>18 pax</t>
-        </is>
-      </c>
-      <c r="E28" s="32" t="inlineStr">
-        <is>
-          <t>⚠ 1 celiaco</t>
-        </is>
-      </c>
+          <t>35 pax</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr"/>
@@ -4687,17 +4683,17 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Chiesina Basket</t>
+          <t>Basket Loano</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>15 pax</t>
+          <t>18 pax</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
+          <t>⚠ 1 celiaco</t>
         </is>
       </c>
     </row>
@@ -4710,22 +4706,44 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
+          <t>Chiesina Basket</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>15 pax</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
           <t>San Fr. Ittiri</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>12 pax</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr"/>
+      <c r="E31" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A19:E19"/>
@@ -4733,6 +4751,7 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -4270,7 +4270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4324,7 +4324,7 @@
     <row r="5">
       <c r="A5" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ☕ Caffè Micky · 12:30 · 24 coperti</t>
+          <t xml:space="preserve">  ☕ Caffè Micky · 12:30 · 33 coperti</t>
         </is>
       </c>
     </row>
@@ -4348,81 +4348,77 @@
       <c r="E6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Shoemakers</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>9 pax</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 42 coperti · ⚠ allergie</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Chiesina Basket</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>15 pax</t>
-        </is>
-      </c>
-      <c r="E8" s="32" t="inlineStr">
-        <is>
-          <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Chiesina Basket</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>15 pax</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>U13</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Dany Basket</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>27 pax</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  ☕ Caffè Micky · 14:00 · 40 coperti · ⚠ allergie</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>TissIttiri</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>24 pax</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
         </is>
       </c>
     </row>
@@ -4435,43 +4431,43 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
+          <t>TissIttiri</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>24 pax</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
           <t>Basket Marsciano</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>16 pax</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🍽 Pool Bar · 14:00 · 101 coperti · ⚠ allergie</t>
-        </is>
-      </c>
+      <c r="E13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Mens Sana Siena</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>36 pax</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>⚠ 1 celiaco</t>
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🍽 Pool Bar · 14:00 · 121 coperti · ⚠ allergie</t>
         </is>
       </c>
     </row>
@@ -4484,38 +4480,38 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Codigoro Basket</t>
+          <t>Mens Sana Siena</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>35 pax</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr"/>
+          <t>36 pax</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Basket Loano</t>
+          <t>Codigoro Basket</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>18 pax</t>
-        </is>
-      </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>⚠ 1 celiaco</t>
-        </is>
-      </c>
+          <t>35 pax</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr"/>
@@ -4526,106 +4522,114 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
+          <t>Basket Loano</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>18 pax</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
           <t>San Fr. Ittiri</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>12 pax</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Shoemakers</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>9 pax</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr"/>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>La T Gema</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>11 pax</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  GIORNO 2 — Sabato 2 Maggio</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="30" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  ☕ Caffè Micky · 12:30 · 16 coperti</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>U13</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Basket Marsciano</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>16 pax</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 24 coperti · ⚠ allergie</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>TissIttiri</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>24 pax</t>
-        </is>
-      </c>
-      <c r="E23" s="32" t="inlineStr">
-        <is>
-          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ☕ Caffè Micky · 13:30 · 35 coperti · ⚠ allergie</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Mens Sana Siena</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>4 pax</t>
-        </is>
-      </c>
-      <c r="E25" s="32" t="inlineStr">
-        <is>
-          <t>⚠ 1 celiaco</t>
         </is>
       </c>
     </row>
@@ -4638,20 +4642,24 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Dany Basket</t>
+          <t>TissIttiri</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>31 pax</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr"/>
+          <t>24 pax</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🍽 Pool Bar · 13:30 · 80 coperti · ⚠ allergie</t>
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ☕ Caffè Micky · 13:30 · 35 coperti · ⚠ allergie</t>
         </is>
       </c>
     </row>
@@ -4664,92 +4672,141 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Codigoro Basket</t>
+          <t>Mens Sana Siena</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>35 pax</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr"/>
+          <t>4 pax</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr"/>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Basket Loano</t>
+          <t>Dany Basket</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>18 pax</t>
-        </is>
-      </c>
-      <c r="E29" s="32" t="inlineStr">
-        <is>
-          <t>⚠ 1 celiaco</t>
-        </is>
-      </c>
+          <t>31 pax</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr"/>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Chiesina Basket</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>15 pax</t>
-        </is>
-      </c>
-      <c r="E30" s="32" t="inlineStr">
-        <is>
-          <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🍽 Pool Bar · 13:30 · 80 coperti · ⚠ allergie</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr"/>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Codigoro Basket</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>35 pax</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr"/>
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Basket Loano</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>18 pax</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr"/>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Chiesina Basket</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>15 pax</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>San Fr. Ittiri</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>12 pax</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr"/>
+      <c r="E34" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A8:E8"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -106,7 +106,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -136,6 +136,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E8"/>
       </patternFill>
     </fill>
     <fill>
@@ -195,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -227,25 +232,28 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,28 +277,28 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -930,9 +938,9 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>54 – 48</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -1147,40 +1155,40 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr"/>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Giorno 1</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Ven 1 Mag</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>15:00–15:45</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>TUTTI</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>CERIMONIA DI APERTURA</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr"/>
-      <c r="I14" s="13" t="inlineStr"/>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr"/>
+      <c r="I14" s="14" t="inlineStr"/>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>🎉 Presentazione squadre, autorità, inno</t>
         </is>
@@ -2037,7 +2045,7 @@
           <t>2°B13</t>
         </is>
       </c>
-      <c r="J33" s="14" t="inlineStr">
+      <c r="J33" s="15" t="inlineStr">
         <is>
           <t>Semifinale Oro U13</t>
         </is>
@@ -2087,7 +2095,7 @@
           <t>2°B14</t>
         </is>
       </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="J34" s="15" t="inlineStr">
         <is>
           <t>Semifinale Oro U14</t>
         </is>
@@ -2137,7 +2145,7 @@
           <t>4°B13</t>
         </is>
       </c>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="J35" s="15" t="inlineStr">
         <is>
           <t>Semifinale Bronzo U13</t>
         </is>
@@ -2187,7 +2195,7 @@
           <t>4°B14</t>
         </is>
       </c>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="J36" s="15" t="inlineStr">
         <is>
           <t>Semifinale Bronzo U14</t>
         </is>
@@ -2237,7 +2245,7 @@
           <t>2°A13</t>
         </is>
       </c>
-      <c r="J37" s="14" t="inlineStr">
+      <c r="J37" s="15" t="inlineStr">
         <is>
           <t>Semifinale Oro U13</t>
         </is>
@@ -2287,7 +2295,7 @@
           <t>2°A14</t>
         </is>
       </c>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="J38" s="15" t="inlineStr">
         <is>
           <t>Semifinale Oro U14</t>
         </is>
@@ -2337,7 +2345,7 @@
           <t>4°A13</t>
         </is>
       </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="J39" s="15" t="inlineStr">
         <is>
           <t>Semifinale Bronzo U13</t>
         </is>
@@ -2387,7 +2395,7 @@
           <t>4°A14</t>
         </is>
       </c>
-      <c r="J40" s="14" t="inlineStr">
+      <c r="J40" s="15" t="inlineStr">
         <is>
           <t>Semifinale Bronzo U14</t>
         </is>
@@ -2444,7 +2452,7 @@
           <t>Perd.SF-Oro2</t>
         </is>
       </c>
-      <c r="J43" s="14" t="inlineStr">
+      <c r="J43" s="15" t="inlineStr">
         <is>
           <t>Finale 3°/4° U13</t>
         </is>
@@ -2494,7 +2502,7 @@
           <t>Perd.SF-Bronzo2</t>
         </is>
       </c>
-      <c r="J44" s="14" t="inlineStr">
+      <c r="J44" s="15" t="inlineStr">
         <is>
           <t>Finale 7°/8° U13</t>
         </is>
@@ -2544,7 +2552,7 @@
           <t>Vinc.SF-Bronzo2</t>
         </is>
       </c>
-      <c r="J45" s="14" t="inlineStr">
+      <c r="J45" s="15" t="inlineStr">
         <is>
           <t>Finale 5°/6° U13</t>
         </is>
@@ -2594,7 +2602,7 @@
           <t>Perd.SF-Oro2</t>
         </is>
       </c>
-      <c r="J46" s="14" t="inlineStr">
+      <c r="J46" s="15" t="inlineStr">
         <is>
           <t>Finale 3°/4° U14</t>
         </is>
@@ -2644,7 +2652,7 @@
           <t>Perd.SF-Bronzo2</t>
         </is>
       </c>
-      <c r="J47" s="14" t="inlineStr">
+      <c r="J47" s="15" t="inlineStr">
         <is>
           <t>Finale 7°/8° U14</t>
         </is>
@@ -2694,7 +2702,7 @@
           <t>Vinc.SF-Bronzo2</t>
         </is>
       </c>
-      <c r="J48" s="14" t="inlineStr">
+      <c r="J48" s="15" t="inlineStr">
         <is>
           <t>Finale 5°/6° U14</t>
         </is>
@@ -2729,7 +2737,7 @@
           <t>U13</t>
         </is>
       </c>
-      <c r="G49" s="15" t="inlineStr">
+      <c r="G49" s="16" t="inlineStr">
         <is>
           <t>Vinc.SF-Oro1</t>
         </is>
@@ -2744,7 +2752,7 @@
           <t>Vinc.SF-Oro2</t>
         </is>
       </c>
-      <c r="J49" s="14" t="inlineStr">
+      <c r="J49" s="15" t="inlineStr">
         <is>
           <t>🏆 FINALISSIMA 1°/2° U13</t>
         </is>
@@ -2779,7 +2787,7 @@
           <t>U14</t>
         </is>
       </c>
-      <c r="G50" s="15" t="inlineStr">
+      <c r="G50" s="16" t="inlineStr">
         <is>
           <t>Vinc.SF-Oro1</t>
         </is>
@@ -2794,47 +2802,47 @@
           <t>Vinc.SF-Oro2</t>
         </is>
       </c>
-      <c r="J50" s="14" t="inlineStr">
+      <c r="J50" s="15" t="inlineStr">
         <is>
           <t>🏆 FINALISSIMA 1°/2° U14</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr"/>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="A51" s="12" t="inlineStr"/>
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>Giorno 3</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>Dom 3 Mag</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>17:00–17:45</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>TUTTI</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t>CERIMONIA DI CHIUSURA</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr"/>
-      <c r="I51" s="13" t="inlineStr"/>
-      <c r="J51" s="13" t="inlineStr">
+      <c r="H51" s="12" t="inlineStr"/>
+      <c r="I51" s="14" t="inlineStr"/>
+      <c r="J51" s="14" t="inlineStr">
         <is>
           <t>🏆 Premiazioni di tutte le categorie</t>
         </is>
@@ -2922,7 +2930,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2946,12 +2954,12 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2975,12 +2983,12 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3004,12 +3012,12 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3033,7 +3041,7 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3045,7 +3053,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3069,12 +3077,12 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3098,12 +3106,12 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3127,12 +3135,12 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3156,7 +3164,7 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3168,7 +3176,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3192,12 +3200,12 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3221,12 +3229,12 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="G18" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3250,12 +3258,12 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3279,7 +3287,7 @@
           <t>0–0</t>
         </is>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3291,118 +3299,118 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
+          <t>Basket Fucecchio</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>54–48</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Chiesina Basket</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>48–54</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
           <t>La T Gema Montecatini</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>0–0</t>
         </is>
       </c>
-      <c r="G23" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="G25" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>San Francesco Ittiri</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="C26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>0–0</t>
         </is>
       </c>
-      <c r="G24" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Chiesina Basket</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Basket Fucecchio</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="n">
+      <c r="G26" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3476,7 +3484,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
@@ -3503,7 +3511,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
@@ -3530,12 +3538,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Nestor Basket Marsciano  ✈️ FUORI REGIONE</t>
         </is>
@@ -3557,12 +3565,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Tissi Ittiri  ✈️ FUORI REGIONE</t>
         </is>
@@ -3591,7 +3599,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
@@ -3618,7 +3626,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
@@ -3645,12 +3653,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Codigoro Basket La Fenice  ✈️ FUORI REGIONE</t>
         </is>
@@ -3672,7 +3680,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
@@ -3706,7 +3714,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
@@ -3733,12 +3741,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Basket Loano  ✈️ FUORI REGIONE</t>
         </is>
@@ -3760,7 +3768,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
@@ -3787,7 +3795,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>E4</t>
         </is>
@@ -3821,7 +3829,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -3848,12 +3856,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>San Francesco Ittiri  ✈️ FUORI REGIONE</t>
         </is>
@@ -3875,7 +3883,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
@@ -3902,7 +3910,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
@@ -3996,22 +4004,22 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Piazza Sandro Pertini · Monsummano Terme</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Palazzetto principale. Entrambe le finalissime (U13 ore 13, U14 ore 15) + cerimonie apertura (ven 15:00) e chiusura (dom 17:00).</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
@@ -4038,7 +4046,7 @@
           <t>Palestra Comunale.</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
@@ -4065,7 +4073,7 @@
           <t>Palestra del Liceo Scientifico Coluccio Salutati.</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
@@ -4077,76 +4085,76 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Piazza Sandro Pertini · Monsummano Terme</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Struttura adiacente al PalaCardelli, stessa piazza.</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>🍽</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Pool Bar</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Piazza Sandro Pertini · Monsummano Terme</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>Punto di ristoro ufficiale per i pranzi. Stessa piazza del PalaCardelli.</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>☕</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Caffè Micky</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>Cintolese · Monsummano Terme</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>Punto di ristoro ufficiale per i pranzi delle squadre che giocano alla Pal. Cintolese.</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
@@ -4213,44 +4221,44 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>🎉 CERIMONIA DI APERTURA</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Ven 1 Maggio</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>15:00 – 15:45</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>🏆 CERIMONIA DI CHIUSURA</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Dom 3 Maggio</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>17:00 – 17:45</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
@@ -4322,7 +4330,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  ☕ Caffè Micky · 12:30 · 33 coperti</t>
         </is>
@@ -4367,7 +4375,7 @@
       <c r="E7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 42 coperti · ⚠ allergie</t>
         </is>
@@ -4390,7 +4398,7 @@
           <t>15 pax</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
         </is>
@@ -4416,7 +4424,7 @@
       <c r="E10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  ☕ Caffè Micky · 14:00 · 40 coperti · ⚠ allergie</t>
         </is>
@@ -4439,7 +4447,7 @@
           <t>24 pax</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
         </is>
@@ -4465,7 +4473,7 @@
       <c r="E13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  🍽 Pool Bar · 14:00 · 121 coperti · ⚠ allergie</t>
         </is>
@@ -4488,7 +4496,7 @@
           <t>36 pax</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco</t>
         </is>
@@ -4530,7 +4538,7 @@
           <t>18 pax</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco</t>
         </is>
@@ -4601,7 +4609,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  ☕ Caffè Micky · 12:30 · 16 coperti</t>
         </is>
@@ -4627,7 +4635,7 @@
       <c r="E24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 24 coperti · ⚠ allergie</t>
         </is>
@@ -4650,14 +4658,14 @@
           <t>24 pax</t>
         </is>
       </c>
-      <c r="E26" s="32" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  ☕ Caffè Micky · 13:30 · 35 coperti · ⚠ allergie</t>
         </is>
@@ -4680,7 +4688,7 @@
           <t>4 pax</t>
         </is>
       </c>
-      <c r="E28" s="32" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco</t>
         </is>
@@ -4706,7 +4714,7 @@
       <c r="E29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  🍽 Pool Bar · 13:30 · 80 coperti · ⚠ allergie</t>
         </is>
@@ -4748,7 +4756,7 @@
           <t>18 pax</t>
         </is>
       </c>
-      <c r="E32" s="32" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco</t>
         </is>
@@ -4771,7 +4779,7 @@
           <t>15 pax</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
         </is>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -3335,25 +3335,25 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Chiesina Basket</t>
+          <t>La T Gema Montecatini</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>48–54</t>
+          <t>0–0</t>
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>La T Gema Montecatini</t>
+          <t>San Francesco Ittiri</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -3393,21 +3393,21 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>San Francesco Ittiri</t>
+          <t>Chiesina Basket</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>48–54</t>
         </is>
       </c>
       <c r="G26" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -135,12 +135,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDDDD"/>
+        <fgColor rgb="00FFF8E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E8"/>
+        <fgColor rgb="00FFDDDD"/>
       </patternFill>
     </fill>
     <fill>
@@ -229,10 +229,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -262,7 +262,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -838,9 +838,9 @@
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>84 – 41</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -878,7 +878,7 @@
           <t>Pal. Liceo Salutati</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -928,7 +928,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -938,7 +938,7 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>54 – 48</t>
         </is>
@@ -1078,7 +1078,7 @@
           <t>Pal. Liceo Salutati</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1128,7 +1128,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1318,7 +1318,7 @@
           <t>Pal. Liceo Salutati</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1368,7 +1368,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1418,7 +1418,7 @@
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1568,7 +1568,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1725,7 +1725,7 @@
           <t>Pal. Liceo Salutati</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1775,7 +1775,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1825,7 +1825,7 @@
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1975,7 +1975,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2075,7 +2075,7 @@
           <t>Pal. Cintolese</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2175,7 +2175,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2275,7 +2275,7 @@
           <t>Pal. Cintolese</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2375,7 +2375,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2582,7 +2582,7 @@
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2632,7 +2632,7 @@
           <t>Pal. Cintolese</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2682,7 +2682,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2782,7 +2782,7 @@
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2932,7 +2932,7 @@
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -2941,32 +2941,32 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>84–41</t>
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Endas Pistoia</t>
+          <t>Nestor Basket Marsciano</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -2990,12 +2990,12 @@
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Nestor Basket Marsciano</t>
+          <t>Tissi Ittiri</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -3019,26 +3019,26 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Tissi Ittiri</t>
+          <t>Endas Pistoia</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>41–84</t>
         </is>
       </c>
       <c r="G8" s="18" t="n">
@@ -4383,7 +4383,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4584,7 +4584,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4741,7 +4741,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr"/>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr"/>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4787,7 +4787,7 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr"/>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>U14</t>
         </is>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -888,9 +888,9 @@
           <t>Basket Calcinaia</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>71 – 34</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -3178,41 +3178,41 @@
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers Monsummano</t>
+          <t>Basket Calcinaia</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>71–34</t>
         </is>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Basket Loano</t>
+          <t>Shoemakers Monsummano</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -3236,12 +3236,12 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Basket Calcinaia</t>
+          <t>Basket Loano</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -3265,7 +3265,7 @@
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3274,17 +3274,17 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>34–71</t>
         </is>
       </c>
       <c r="G20" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -226,13 +226,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -790,7 +790,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>0 – 0</t>
+          <t>21 – 108</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -838,7 +838,7 @@
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>84 – 41</t>
         </is>
@@ -878,7 +878,7 @@
           <t>Pal. Liceo Salutati</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -888,7 +888,7 @@
           <t>Basket Calcinaia</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>71 – 34</t>
         </is>
@@ -928,7 +928,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -938,7 +938,7 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>54 – 48</t>
         </is>
@@ -988,7 +988,7 @@
           <t>Codigoro Basket</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1038,7 +1038,7 @@
           <t>Basket Marsciano</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1078,7 +1078,7 @@
           <t>Pal. Liceo Salutati</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1088,7 +1088,7 @@
           <t>Basket Loano</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1128,7 +1128,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1138,7 +1138,7 @@
           <t>La T Gema</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1228,7 +1228,7 @@
           <t>Basket Marsciano</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1278,7 +1278,7 @@
           <t>Mens Sana Siena</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1318,7 +1318,7 @@
           <t>Pal. Liceo Salutati</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1328,7 +1328,7 @@
           <t>Basket Calcinaia</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1368,7 +1368,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1378,7 +1378,7 @@
           <t>Chiesina Basket</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1418,7 +1418,7 @@
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1428,7 +1428,7 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1478,7 +1478,7 @@
           <t>Endas Pistoia</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1528,7 +1528,7 @@
           <t>Codigoro Basket</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1568,7 +1568,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1578,7 +1578,7 @@
           <t>Basket Loano</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1635,7 +1635,7 @@
           <t>Codigoro Basket</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1685,7 +1685,7 @@
           <t>Basket Marsciano</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1725,7 +1725,7 @@
           <t>Pal. Liceo Salutati</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1735,7 +1735,7 @@
           <t>Massa e Cozzile</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1775,7 +1775,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1785,7 +1785,7 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1825,7 +1825,7 @@
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1835,7 +1835,7 @@
           <t>Basket Calcinaia</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1885,7 +1885,7 @@
           <t>Dany Basket</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1935,7 +1935,7 @@
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1975,7 +1975,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -1985,7 +1985,7 @@
           <t>Chiesina Basket</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -2035,7 +2035,7 @@
           <t>1°A13</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2075,7 +2075,7 @@
           <t>Pal. Cintolese</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2085,7 +2085,7 @@
           <t>1°A14</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2135,7 +2135,7 @@
           <t>3°A13</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2175,7 +2175,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2185,7 +2185,7 @@
           <t>3°A14</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2235,7 +2235,7 @@
           <t>1°B13</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2275,7 +2275,7 @@
           <t>Pal. Cintolese</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2285,7 +2285,7 @@
           <t>1°B14</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2335,7 +2335,7 @@
           <t>3°B13</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2375,7 +2375,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2385,7 +2385,7 @@
           <t>3°B14</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2442,7 +2442,7 @@
           <t>Perd.SF-Oro1</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2492,7 +2492,7 @@
           <t>Perd.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2542,7 +2542,7 @@
           <t>Vinc.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2582,7 +2582,7 @@
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2592,7 +2592,7 @@
           <t>Perd.SF-Oro1</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2632,7 +2632,7 @@
           <t>Pal. Cintolese</t>
         </is>
       </c>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2642,7 +2642,7 @@
           <t>Perd.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H47" s="9" t="inlineStr">
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2682,7 +2682,7 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2692,7 +2692,7 @@
           <t>Vinc.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H48" s="9" t="inlineStr">
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2742,7 +2742,7 @@
           <t>Vinc.SF-Oro1</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2782,7 +2782,7 @@
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -2792,7 +2792,7 @@
           <t>Vinc.SF-Oro1</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3055,41 +3055,41 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Mens Sana Siena</t>
+          <t>Prato Dragons Basket</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>108–21</t>
         </is>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Prato Dragons Basket</t>
+          <t>Mens Sana Siena</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -3113,7 +3113,7 @@
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -3151,17 +3151,17 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>21–108</t>
         </is>
       </c>
       <c r="G14" s="18" t="n">
@@ -4383,7 +4383,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4584,7 +4584,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4741,7 +4741,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr"/>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr"/>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
@@ -4787,7 +4787,7 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr"/>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1138,9 +1138,9 @@
           <t>La T Gema</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>71 – 55</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Basket Fucecchio</t>
+          <t>La T Gema Montecatini</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>54–48</t>
+          <t>71–55</t>
         </is>
       </c>
       <c r="G23" s="18" t="n">
@@ -3335,25 +3335,25 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>La T Gema Montecatini</t>
+          <t>Basket Fucecchio</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>54–48</t>
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -3364,21 +3364,21 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>San Francesco Ittiri</t>
+          <t>Chiesina Basket</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>48–54</t>
         </is>
       </c>
       <c r="G25" s="18" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Chiesina Basket</t>
+          <t>San Francesco Ittiri</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>48–54</t>
+          <t>55–71</t>
         </is>
       </c>
       <c r="G26" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1088,9 +1088,9 @@
           <t>Basket Loano</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>42 – 66</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
@@ -3216,21 +3216,21 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>66–42</t>
         </is>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3245,17 +3245,17 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>42–66</t>
         </is>
       </c>
       <c r="G19" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1038,9 +1038,9 @@
           <t>Basket Marsciano</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>68 – 44</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>68–44</t>
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2999,17 +2999,17 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>44–68</t>
         </is>
       </c>
       <c r="G7" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -232,9 +232,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -243,6 +240,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -988,9 +988,9 @@
           <t>Codigoro Basket</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>79 – 57</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
@@ -1155,40 +1155,40 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr"/>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr"/>
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Giorno 1</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Ven 1 Mag</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>15:00–15:45</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>TUTTI</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>CERIMONIA DI APERTURA</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="14" t="inlineStr"/>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr"/>
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>🎉 Presentazione squadre, autorità, inno</t>
         </is>
@@ -1228,7 +1228,7 @@
           <t>Basket Marsciano</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1278,7 +1278,7 @@
           <t>Mens Sana Siena</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1328,7 +1328,7 @@
           <t>Basket Calcinaia</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1378,7 +1378,7 @@
           <t>Chiesina Basket</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1428,7 +1428,7 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1478,7 +1478,7 @@
           <t>Endas Pistoia</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1528,7 +1528,7 @@
           <t>Codigoro Basket</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1578,7 +1578,7 @@
           <t>Basket Loano</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1635,7 +1635,7 @@
           <t>Codigoro Basket</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1685,7 +1685,7 @@
           <t>Basket Marsciano</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1735,7 +1735,7 @@
           <t>Massa e Cozzile</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1785,7 +1785,7 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1835,7 +1835,7 @@
           <t>Basket Calcinaia</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1885,7 +1885,7 @@
           <t>Dany Basket</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1935,7 +1935,7 @@
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -1985,7 +1985,7 @@
           <t>Chiesina Basket</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -2035,7 +2035,7 @@
           <t>1°A13</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2085,7 +2085,7 @@
           <t>1°A14</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H34" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2135,7 +2135,7 @@
           <t>3°A13</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2185,7 +2185,7 @@
           <t>3°A14</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H36" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2235,7 +2235,7 @@
           <t>1°B13</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2285,7 +2285,7 @@
           <t>1°B14</t>
         </is>
       </c>
-      <c r="H38" s="11" t="inlineStr">
+      <c r="H38" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2335,7 +2335,7 @@
           <t>3°B13</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2385,7 +2385,7 @@
           <t>3°B14</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2442,7 +2442,7 @@
           <t>Perd.SF-Oro1</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2492,7 +2492,7 @@
           <t>Perd.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H44" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2542,7 +2542,7 @@
           <t>Vinc.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H45" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2592,7 +2592,7 @@
           <t>Perd.SF-Oro1</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
+      <c r="H46" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2642,7 +2642,7 @@
           <t>Perd.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H47" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2692,7 +2692,7 @@
           <t>Vinc.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H48" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2742,7 +2742,7 @@
           <t>Vinc.SF-Oro1</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="H49" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2792,7 +2792,7 @@
           <t>Vinc.SF-Oro1</t>
         </is>
       </c>
-      <c r="H50" s="11" t="inlineStr">
+      <c r="H50" s="14" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2809,40 +2809,40 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr"/>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr"/>
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>Giorno 3</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>Dom 3 Mag</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>17:00–17:45</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>TUTTI</t>
         </is>
       </c>
-      <c r="G51" s="13" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>CERIMONIA DI CHIUSURA</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr"/>
-      <c r="I51" s="14" t="inlineStr"/>
-      <c r="J51" s="14" t="inlineStr">
+      <c r="H51" s="11" t="inlineStr"/>
+      <c r="I51" s="13" t="inlineStr"/>
+      <c r="J51" s="13" t="inlineStr">
         <is>
           <t>🏆 Premiazioni di tutte le categorie</t>
         </is>
@@ -3089,25 +3089,25 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Mens Sana Siena</t>
+          <t>Codigoro Basket La Fenice</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>79–57</t>
         </is>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -3118,21 +3118,21 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Codigoro Basket La Fenice</t>
+          <t>Mens Sana Siena</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>57–79</t>
         </is>
       </c>
       <c r="G13" s="18" t="n">
@@ -4221,7 +4221,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>🎉 CERIMONIA DI APERTURA</t>
         </is>
@@ -4243,7 +4243,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>🏆 CERIMONIA DI CHIUSURA</t>
         </is>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -4637,7 +4637,7 @@
     <row r="25">
       <c r="A25" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 24 coperti · ⚠ allergie</t>
+          <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 35 coperti</t>
         </is>
       </c>
     </row>
@@ -4650,19 +4650,15 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>TissIttiri</t>
+          <t>Codigoro Basket</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>24 pax</t>
-        </is>
-      </c>
-      <c r="E26" s="33" t="inlineStr">
-        <is>
-          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
-        </is>
-      </c>
+          <t>35 pax</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
@@ -4716,7 +4712,7 @@
     <row r="30">
       <c r="A30" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🍽 Pool Bar · 13:30 · 80 coperti · ⚠ allergie</t>
+          <t xml:space="preserve">  🍽 Pool Bar · 13:30 · 69 coperti · ⚠ allergie</t>
         </is>
       </c>
     </row>
@@ -4729,15 +4725,19 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Codigoro Basket</t>
+          <t>TissIttiri</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>35 pax</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr"/>
+          <t>24 pax</t>
+        </is>
+      </c>
+      <c r="E31" s="33" t="inlineStr">
+        <is>
+          <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr"/>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1378,9 +1378,9 @@
           <t>Chiesina Basket</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>82 – 64</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
@@ -3306,21 +3306,21 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>La T Gema Montecatini</t>
+          <t>Chiesina Basket</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>71–55</t>
+          <t>130–118</t>
         </is>
       </c>
       <c r="G23" s="18" t="n">
@@ -3364,25 +3364,25 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Chiesina Basket</t>
+          <t>La T Gema Montecatini</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>48–54</t>
+          <t>135–137</t>
         </is>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1228,9 +1228,9 @@
           <t>Basket Marsciano</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>45 – 50</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>84–41</t>
+          <t>134–86</t>
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2970,17 +2970,17 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>68–44</t>
+          <t>113–94</t>
         </is>
       </c>
       <c r="G6" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1278,9 +1278,9 @@
           <t>Mens Sana Siena</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>52 – 77</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>108–21</t>
+          <t>185–73</t>
         </is>
       </c>
       <c r="G11" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -3122,17 +3122,17 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>57–79</t>
+          <t>109–156</t>
         </is>
       </c>
       <c r="G13" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1328,9 +1328,9 @@
           <t>Basket Calcinaia</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>33 – 92</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
@@ -3183,25 +3183,25 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Basket Calcinaia</t>
+          <t>Shoemakers Monsummano</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>71–34</t>
+          <t>158–75</t>
         </is>
       </c>
       <c r="G17" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -3212,21 +3212,21 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers Monsummano</t>
+          <t>Basket Calcinaia</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>66–42</t>
+          <t>104–126</t>
         </is>
       </c>
       <c r="G18" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1428,9 +1428,9 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>67 – 53</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
@@ -3306,25 +3306,25 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Chiesina Basket</t>
+          <t>Basket Fucecchio</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>130–118</t>
+          <t>121–101</t>
         </is>
       </c>
       <c r="G23" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -3335,21 +3335,21 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Basket Fucecchio</t>
+          <t>Chiesina Basket</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>54–48</t>
+          <t>130–118</t>
         </is>
       </c>
       <c r="G24" s="18" t="n">
@@ -3397,17 +3397,17 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>55–71</t>
+          <t>108–138</t>
         </is>
       </c>
       <c r="G26" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1578,9 +1578,9 @@
           <t>Basket Loano</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>71 – 36</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Basket Calcinaia</t>
+          <t>Basket Loano</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>104–126</t>
+          <t>113–102</t>
         </is>
       </c>
       <c r="G18" s="18" t="n">
@@ -3241,25 +3241,25 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Basket Loano</t>
+          <t>Basket Calcinaia</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>42–66</t>
+          <t>104–126</t>
         </is>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -3274,17 +3274,17 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>34–71</t>
+          <t>70–142</t>
         </is>
       </c>
       <c r="G20" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1478,9 +1478,9 @@
           <t>Endas Pistoia</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>53 – 70</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
@@ -2999,21 +2999,21 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>44–68</t>
+          <t>114–121</t>
         </is>
       </c>
       <c r="G7" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3028,17 +3028,17 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>41–84</t>
+          <t>94–154</t>
         </is>
       </c>
       <c r="G8" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1528,9 +1528,9 @@
           <t>Codigoro Basket</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>96 – 39</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>79–57</t>
+          <t>175–96</t>
         </is>
       </c>
       <c r="G12" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -3151,17 +3151,17 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>21–108</t>
+          <t>60–204</t>
         </is>
       </c>
       <c r="G14" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2172,17 +2172,17 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Geodetica</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+          <t>Pal. Liceo Salutati</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>3°A14</t>
+          <t>3°B13</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>4°B14</t>
+          <t>4°A13</t>
         </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>Semifinale Bronzo U14</t>
+          <t>Semifinale Bronzo U13</t>
         </is>
       </c>
     </row>
@@ -2322,17 +2322,17 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Pal. Liceo Salutati</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+          <t>Geodetica</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>3°B13</t>
+          <t>3°A14</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>4°A13</t>
+          <t>4°B14</t>
         </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
         <is>
-          <t>Semifinale Bronzo U13</t>
+          <t>Semifinale Bronzo U14</t>
         </is>
       </c>
     </row>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1735,9 +1735,9 @@
           <t>Massa e Cozzile</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>29 – 109</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -3187,21 +3187,21 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>158–75</t>
+          <t>267–104</t>
         </is>
       </c>
       <c r="G17" s="18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -3274,17 +3274,17 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>70–142</t>
+          <t>99–251</t>
         </is>
       </c>
       <c r="G20" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1635,9 +1635,9 @@
           <t>Codigoro Basket</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>36 – 39</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>185–73</t>
+          <t>224–109</t>
         </is>
       </c>
       <c r="G11" s="18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -3093,17 +3093,17 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>175–96</t>
+          <t>211–135</t>
         </is>
       </c>
       <c r="G12" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1785,9 +1785,9 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>45 – 64</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -3306,21 +3306,21 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Basket Fucecchio</t>
+          <t>La T Gema Montecatini</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>121–101</t>
+          <t>199–182</t>
         </is>
       </c>
       <c r="G23" s="18" t="n">
@@ -3335,25 +3335,25 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Chiesina Basket</t>
+          <t>Basket Fucecchio</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>130–118</t>
+          <t>166–165</t>
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>La T Gema Montecatini</t>
+          <t>Chiesina Basket</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>135–137</t>
+          <t>130–118</t>
         </is>
       </c>
       <c r="G25" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1685,9 +1685,9 @@
           <t>Basket Marsciano</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>66 – 48</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>113–94</t>
+          <t>179–142</t>
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3028,17 +3028,17 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>94–154</t>
+          <t>142–220</t>
         </is>
       </c>
       <c r="G8" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2042,7 +2042,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>2°B13</t>
+          <t>Codigoro Basket</t>
         </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>1°A14</t>
+          <t>Shoemakers</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>4°A13</t>
+          <t>Endas Pistoia</t>
         </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>1°B13</t>
+          <t>Prato Dragons</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>4°A14</t>
+          <t>Massa e Cozzile</t>
         </is>
       </c>
       <c r="J40" s="15" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2172,17 +2172,17 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Pal. Liceo Salutati</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+          <t>Geodetica</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>3°B13</t>
+          <t>3°A14</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>Endas Pistoia</t>
+          <t>4°B14</t>
         </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>Semifinale Bronzo U13</t>
+          <t>Semifinale Bronzo U14</t>
         </is>
       </c>
     </row>
@@ -2322,17 +2322,17 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Geodetica</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+          <t>Pal. Liceo Salutati</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>3°A14</t>
+          <t>3°B13</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>4°B14</t>
+          <t>Endas Pistoia</t>
         </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
         <is>
-          <t>Semifinale Bronzo U14</t>
+          <t>Semifinale Bronzo U13</t>
         </is>
       </c>
     </row>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2042,7 +2042,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Codigoro Basket</t>
+          <t>2°B13</t>
         </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers</t>
+          <t>1°A14</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Prato Dragons</t>
+          <t>1°B13</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>Endas Pistoia</t>
+          <t>4°A13</t>
         </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>Massa e Cozzile</t>
+          <t>4°A14</t>
         </is>
       </c>
       <c r="J40" s="15" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1935,9 +1935,9 @@
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>74 – 54</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>134–86</t>
+          <t>208–140</t>
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2999,17 +2999,17 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>114–121</t>
+          <t>168–195</t>
         </is>
       </c>
       <c r="G7" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1985,9 +1985,9 @@
           <t>Chiesina Basket</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>68 – 35</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>La T Gema Montecatini</t>
+          <t>Chiesina Basket</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>199–182</t>
+          <t>198–153</t>
         </is>
       </c>
       <c r="G23" s="18" t="n">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Basket Fucecchio</t>
+          <t>La T Gema Montecatini</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>166–165</t>
+          <t>199–182</t>
         </is>
       </c>
       <c r="G24" s="18" t="n">
@@ -3364,25 +3364,25 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Chiesina Basket</t>
+          <t>Basket Fucecchio</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>130–118</t>
+          <t>166–165</t>
         </is>
       </c>
       <c r="G25" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -3397,17 +3397,17 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>108–138</t>
+          <t>143–206</t>
         </is>
       </c>
       <c r="G26" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1885,9 +1885,9 @@
           <t>Dany Basket</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>44 – 70</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -3122,21 +3122,21 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>109–156</t>
+          <t>179–200</t>
         </is>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -3151,17 +3151,17 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>60–204</t>
+          <t>104–274</t>
         </is>
       </c>
       <c r="G14" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -1835,9 +1835,9 @@
           <t>Basket Calcinaia</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>60 – 37</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
@@ -3212,25 +3212,25 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Basket Loano</t>
+          <t>Basket Calcinaia</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>113–102</t>
+          <t>164–163</t>
         </is>
       </c>
       <c r="G18" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -3241,21 +3241,21 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Basket Calcinaia</t>
+          <t>Basket Loano</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>104–126</t>
+          <t>150–162</t>
         </is>
       </c>
       <c r="G19" s="18" t="n">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>3°A13</t>
+          <t>3°B13</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>4°B13</t>
+          <t>4°A13</t>
         </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>3°B13</t>
+          <t>3°A13</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>4°A13</t>
+          <t>4°B13</t>
         </is>
       </c>
       <c r="J39" s="15" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2032,7 +2032,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>1°A13</t>
+          <t>Shoemakers</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>2°B13</t>
+          <t>Codigoro Basket</t>
         </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>1°A14</t>
+          <t>Shoemakers</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>2°B14</t>
+          <t>La T Gema</t>
         </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>3°B13</t>
+          <t>Mens Sana Siena</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>4°A13</t>
+          <t>Endas Pistoia</t>
         </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>3°A14</t>
+          <t>Basket Loano</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>4°B14</t>
+          <t>San Fr. Ittiri</t>
         </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>1°B13</t>
+          <t>Prato Dragons</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>2°A13</t>
+          <t>Basket Marsciano</t>
         </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>1°B14</t>
+          <t>Chiesina Basket</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>2°A14</t>
+          <t>Basket Calcinaia</t>
         </is>
       </c>
       <c r="J38" s="15" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>3°A13</t>
+          <t>TissIttiri</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>4°B13</t>
+          <t>Dany Basket</t>
         </is>
       </c>
       <c r="J39" s="15" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>3°B14</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>4°A14</t>
+          <t>Massa e Cozzile</t>
         </is>
       </c>
       <c r="J40" s="15" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2175,14 +2175,14 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Basket Loano</t>
+          <t>Prato Dragons</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>San Fr. Ittiri</t>
+          <t>Basket Marsciano</t>
         </is>
       </c>
       <c r="J36" s="15" t="inlineStr">
         <is>
-          <t>Semifinale Bronzo U14</t>
+          <t>Semifinale Oro U13</t>
         </is>
       </c>
     </row>
@@ -2225,14 +2225,14 @@
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Prato Dragons</t>
+          <t>Basket Loano</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>Basket Marsciano</t>
+          <t>San Fr. Ittiri</t>
         </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
-          <t>Semifinale Oro U13</t>
+          <t>Semifinale Bronzo U14</t>
         </is>
       </c>
     </row>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2082,7 +2082,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>La T Gema</t>
+          <t>Massa e Cozzile</t>
         </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
-          <t>Semifinale Oro U14</t>
+          <t>Semifinale Bronzo U14</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Fucecchio</t>
+          <t>Shoemakers</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>Massa e Cozzile</t>
+          <t>La T Gema</t>
         </is>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>Semifinale Bronzo U14</t>
+          <t>Semifinale Oro U14</t>
         </is>
       </c>
     </row>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2232,7 +2232,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Basket Loano</t>
+          <t>Shoemakers</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>San Fr. Ittiri</t>
+          <t>La T Gema</t>
         </is>
       </c>
       <c r="J37" s="15" t="inlineStr">
         <is>
-          <t>Semifinale Bronzo U14</t>
+          <t>Semifinale Oro U14</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Shoemakers</t>
+          <t>Basket Loano</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>La T Gema</t>
+          <t>San Fr. Ittiri</t>
         </is>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>Semifinale Oro U14</t>
+          <t>Semifinale Bronzo U14</t>
         </is>
       </c>
     </row>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -241,11 +241,11 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2035,9 +2035,9 @@
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>70 – 66</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
@@ -2045,7 +2045,7 @@
           <t>Codigoro Basket</t>
         </is>
       </c>
-      <c r="J33" s="15" t="inlineStr">
+      <c r="J33" s="14" t="inlineStr">
         <is>
           <t>Semifinale Oro U13</t>
         </is>
@@ -2085,7 +2085,7 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2095,7 +2095,7 @@
           <t>Massa e Cozzile</t>
         </is>
       </c>
-      <c r="J34" s="15" t="inlineStr">
+      <c r="J34" s="14" t="inlineStr">
         <is>
           <t>Semifinale Bronzo U14</t>
         </is>
@@ -2135,7 +2135,7 @@
           <t>Mens Sana Siena</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H35" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2145,7 +2145,7 @@
           <t>Endas Pistoia</t>
         </is>
       </c>
-      <c r="J35" s="15" t="inlineStr">
+      <c r="J35" s="14" t="inlineStr">
         <is>
           <t>Semifinale Bronzo U13</t>
         </is>
@@ -2185,7 +2185,7 @@
           <t>Prato Dragons</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H36" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2195,7 +2195,7 @@
           <t>Basket Marsciano</t>
         </is>
       </c>
-      <c r="J36" s="15" t="inlineStr">
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>Semifinale Oro U13</t>
         </is>
@@ -2235,7 +2235,7 @@
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H37" s="14" t="inlineStr">
+      <c r="H37" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2245,7 +2245,7 @@
           <t>La T Gema</t>
         </is>
       </c>
-      <c r="J37" s="15" t="inlineStr">
+      <c r="J37" s="14" t="inlineStr">
         <is>
           <t>Semifinale Oro U14</t>
         </is>
@@ -2285,7 +2285,7 @@
           <t>Chiesina Basket</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="H38" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2295,7 +2295,7 @@
           <t>Basket Calcinaia</t>
         </is>
       </c>
-      <c r="J38" s="15" t="inlineStr">
+      <c r="J38" s="14" t="inlineStr">
         <is>
           <t>Semifinale Oro U14</t>
         </is>
@@ -2335,7 +2335,7 @@
           <t>TissIttiri</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="H39" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2345,7 +2345,7 @@
           <t>Dany Basket</t>
         </is>
       </c>
-      <c r="J39" s="15" t="inlineStr">
+      <c r="J39" s="14" t="inlineStr">
         <is>
           <t>Semifinale Bronzo U13</t>
         </is>
@@ -2385,7 +2385,7 @@
           <t>Basket Loano</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr">
+      <c r="H40" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2395,7 +2395,7 @@
           <t>San Fr. Ittiri</t>
         </is>
       </c>
-      <c r="J40" s="15" t="inlineStr">
+      <c r="J40" s="14" t="inlineStr">
         <is>
           <t>Semifinale Bronzo U14</t>
         </is>
@@ -2442,7 +2442,7 @@
           <t>Perd.SF-Oro1</t>
         </is>
       </c>
-      <c r="H43" s="14" t="inlineStr">
+      <c r="H43" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2452,7 +2452,7 @@
           <t>Perd.SF-Oro2</t>
         </is>
       </c>
-      <c r="J43" s="15" t="inlineStr">
+      <c r="J43" s="14" t="inlineStr">
         <is>
           <t>Finale 3°/4° U13</t>
         </is>
@@ -2492,7 +2492,7 @@
           <t>Perd.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr">
+      <c r="H44" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2502,7 +2502,7 @@
           <t>Perd.SF-Bronzo2</t>
         </is>
       </c>
-      <c r="J44" s="15" t="inlineStr">
+      <c r="J44" s="14" t="inlineStr">
         <is>
           <t>Finale 7°/8° U13</t>
         </is>
@@ -2542,7 +2542,7 @@
           <t>Vinc.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H45" s="14" t="inlineStr">
+      <c r="H45" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2552,7 +2552,7 @@
           <t>Vinc.SF-Bronzo2</t>
         </is>
       </c>
-      <c r="J45" s="15" t="inlineStr">
+      <c r="J45" s="14" t="inlineStr">
         <is>
           <t>Finale 5°/6° U13</t>
         </is>
@@ -2592,7 +2592,7 @@
           <t>Perd.SF-Oro1</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr">
+      <c r="H46" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2602,7 +2602,7 @@
           <t>Perd.SF-Oro2</t>
         </is>
       </c>
-      <c r="J46" s="15" t="inlineStr">
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>Finale 3°/4° U14</t>
         </is>
@@ -2642,7 +2642,7 @@
           <t>Perd.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr">
+      <c r="H47" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2652,7 +2652,7 @@
           <t>Perd.SF-Bronzo2</t>
         </is>
       </c>
-      <c r="J47" s="15" t="inlineStr">
+      <c r="J47" s="14" t="inlineStr">
         <is>
           <t>Finale 7°/8° U14</t>
         </is>
@@ -2692,7 +2692,7 @@
           <t>Vinc.SF-Bronzo1</t>
         </is>
       </c>
-      <c r="H48" s="14" t="inlineStr">
+      <c r="H48" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2702,7 +2702,7 @@
           <t>Vinc.SF-Bronzo2</t>
         </is>
       </c>
-      <c r="J48" s="15" t="inlineStr">
+      <c r="J48" s="14" t="inlineStr">
         <is>
           <t>Finale 5°/6° U14</t>
         </is>
@@ -2742,7 +2742,7 @@
           <t>Vinc.SF-Oro1</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr">
+      <c r="H49" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2752,7 +2752,7 @@
           <t>Vinc.SF-Oro2</t>
         </is>
       </c>
-      <c r="J49" s="15" t="inlineStr">
+      <c r="J49" s="14" t="inlineStr">
         <is>
           <t>🏆 FINALISSIMA 1°/2° U13</t>
         </is>
@@ -2792,7 +2792,7 @@
           <t>Vinc.SF-Oro1</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="H50" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -2802,7 +2802,7 @@
           <t>Vinc.SF-Oro2</t>
         </is>
       </c>
-      <c r="J50" s="15" t="inlineStr">
+      <c r="J50" s="14" t="inlineStr">
         <is>
           <t>🏆 FINALISSIMA 1°/2° U14</t>
         </is>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2085,9 +2085,9 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H34" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>50 – 45</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2135,9 +2135,9 @@
           <t>Mens Sana Siena</t>
         </is>
       </c>
-      <c r="H35" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>99 – 46</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2185,9 +2185,9 @@
           <t>Prato Dragons</t>
         </is>
       </c>
-      <c r="H36" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>68 – 42</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2235,9 +2235,9 @@
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H37" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>100 – 32</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2385,9 +2385,9 @@
           <t>Basket Loano</t>
         </is>
       </c>
-      <c r="H40" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>68 – 35</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2285,9 +2285,9 @@
           <t>Chiesina Basket</t>
         </is>
       </c>
-      <c r="H38" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>43 – 72</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2335,9 +2335,9 @@
           <t>TissIttiri</t>
         </is>
       </c>
-      <c r="H39" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>70 – 62</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -666,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2432,29 +2432,29 @@
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Perd.SF-Oro1</t>
+          <t>La T Gema</t>
         </is>
       </c>
       <c r="H43" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>0 – 0</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>Perd.SF-Oro2</t>
+          <t>Chiesina Basket</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>Finale 3°/4° U13</t>
+          <t>Finale 3°/4° U14</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Pal. Cintolese</t>
+          <t>Geodetica</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2489,17 +2489,17 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>Perd.SF-Bronzo1</t>
+          <t>Endas Pistoia</t>
         </is>
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>0 – 0</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>Perd.SF-Bronzo2</t>
+          <t>Dany Basket</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
@@ -2524,37 +2524,37 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Geodetica</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
+          <t>Pal. Cintolese</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>Vinc.SF-Bronzo1</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="H45" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>0 – 0</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>Vinc.SF-Bronzo2</t>
-        </is>
-      </c>
-      <c r="J45" s="14" t="inlineStr">
-        <is>
-          <t>Finale 5°/6° U13</t>
+          <t>Basket Loano</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>Mini-torneo 5°-7° U14</t>
         </is>
       </c>
     </row>
@@ -2574,12 +2574,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>🏟 PalaCardelli</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Pal. Cintolese</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
@@ -2589,22 +2589,22 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>Perd.SF-Oro1</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>0 – 0</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>Perd.SF-Oro2</t>
-        </is>
-      </c>
-      <c r="J46" s="14" t="inlineStr">
-        <is>
-          <t>Finale 3°/4° U14</t>
+          <t>San Fr. Ittiri</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>Mini-torneo 5°-7° U14</t>
         </is>
       </c>
     </row>
@@ -2627,34 +2627,34 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>Pal. Cintolese</t>
-        </is>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>Perd.SF-Bronzo1</t>
+          <t>Codigoro Basket</t>
         </is>
       </c>
       <c r="H47" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>0 – 0</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>Perd.SF-Bronzo2</t>
+          <t>Basket Marsciano</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>Finale 7°/8° U14</t>
+          <t>Finale 3°/4° U13</t>
         </is>
       </c>
     </row>
@@ -2682,29 +2682,29 @@
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>U14</t>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>Vinc.SF-Bronzo1</t>
+          <t>Mens Sana Siena</t>
         </is>
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>0 – 0</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Vinc.SF-Bronzo2</t>
+          <t>TissIttiri</t>
         </is>
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>Finale 5°/6° U14</t>
+          <t>Finale 5°/6° U13</t>
         </is>
       </c>
     </row>
@@ -2724,37 +2724,37 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>🏟 PalaCardelli</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>Vinc.SF-Oro1</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Pal. Cintolese</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>Basket Loano</t>
         </is>
       </c>
       <c r="H49" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>0 – 0</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>Vinc.SF-Oro2</t>
-        </is>
-      </c>
-      <c r="J49" s="14" t="inlineStr">
-        <is>
-          <t>🏆 FINALISSIMA 1°/2° U13</t>
+          <t>San Fr. Ittiri</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>Mini-torneo 5°-7° U14</t>
         </is>
       </c>
     </row>
@@ -2774,75 +2774,125 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>🏟 PalaCardelli</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>U13</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>Shoemakers</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>0 – 0</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Prato Dragons</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>🏆 FINALISSIMA 1°/2° U13</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Giorno 3</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Dom 3 Mag</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>U14</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>Vinc.SF-Oro1</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>Vinc.SF-Oro2</t>
-        </is>
-      </c>
-      <c r="J50" s="14" t="inlineStr">
+      <c r="G51" s="16" t="inlineStr">
+        <is>
+          <t>Shoemakers</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="inlineStr">
+        <is>
+          <t>0 – 0</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>Basket Calcinaia</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
         <is>
           <t>🏆 FINALISSIMA 1°/2° U14</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr"/>
-      <c r="B51" s="11" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr"/>
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>Giorno 3</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>Dom 3 Mag</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>17:00–17:45</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>TUTTI</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>CERIMONIA DI CHIUSURA</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr"/>
-      <c r="I51" s="13" t="inlineStr"/>
-      <c r="J51" s="13" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr"/>
+      <c r="I52" s="13" t="inlineStr"/>
+      <c r="J52" s="13" t="inlineStr">
         <is>
           <t>🏆 Premiazioni di tutte le categorie</t>
         </is>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>Mini-torneo 5°-7° U14</t>
+          <t>Mini-torneo 5°-7° U14 (45')</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>Mini-torneo 5°-7° U14</t>
+          <t>Mini-torneo 5°-7° U14 (45')</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>Mini-torneo 5°-7° U14</t>
+          <t>Mini-torneo 5°-7° U14 (45')</t>
         </is>
       </c>
     </row>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2442,9 +2442,9 @@
           <t>La T Gema</t>
         </is>
       </c>
-      <c r="H43" s="15" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>58 – 76</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2492,9 +2492,9 @@
           <t>Endas Pistoia</t>
         </is>
       </c>
-      <c r="H44" s="15" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>47 – 48</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2592,9 +2592,9 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H46" s="15" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>42 – 19</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2742,9 +2742,9 @@
           <t>Basket Loano</t>
         </is>
       </c>
-      <c r="H49" s="15" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>37 – 32</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2692,9 +2692,9 @@
           <t>Mens Sana Siena</t>
         </is>
       </c>
-      <c r="H48" s="15" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>78 – 46</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2642,9 +2642,9 @@
           <t>Codigoro Basket</t>
         </is>
       </c>
-      <c r="H47" s="15" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>67 – 59</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -244,11 +244,11 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2542,9 +2542,9 @@
           <t>Fucecchio</t>
         </is>
       </c>
-      <c r="H45" s="15" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>41 – 21</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
@@ -2787,12 +2787,12 @@
           <t>U13</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="G50" s="15" t="inlineStr">
         <is>
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H50" s="15" t="inlineStr">
+      <c r="H50" s="16" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
@@ -2837,12 +2837,12 @@
           <t>U14</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr">
+      <c r="G51" s="15" t="inlineStr">
         <is>
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H51" s="15" t="inlineStr">
+      <c r="H51" s="16" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -2792,9 +2792,9 @@
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H50" s="16" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>49 – 66</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">

--- a/torneo_programma.xlsx
+++ b/torneo_programma.xlsx
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -246,9 +246,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2842,9 +2839,9 @@
           <t>Shoemakers</t>
         </is>
       </c>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>0 – 0</t>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>66 – 63</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
@@ -2980,7 +2977,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3004,12 +3001,12 @@
           <t>208–140</t>
         </is>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="17" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3033,12 +3030,12 @@
           <t>179–142</t>
         </is>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="17" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3062,12 +3059,12 @@
           <t>168–195</t>
         </is>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3091,7 +3088,7 @@
           <t>142–220</t>
         </is>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3103,7 +3100,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3127,12 +3124,12 @@
           <t>224–109</t>
         </is>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="17" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3156,12 +3153,12 @@
           <t>211–135</t>
         </is>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="17" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3185,12 +3182,12 @@
           <t>179–200</t>
         </is>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3214,7 +3211,7 @@
           <t>104–274</t>
         </is>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3226,7 +3223,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3250,12 +3247,12 @@
           <t>267–104</t>
         </is>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="17" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3279,12 +3276,12 @@
           <t>164–163</t>
         </is>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="17" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3308,12 +3305,12 @@
           <t>150–162</t>
         </is>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3337,7 +3334,7 @@
           <t>99–251</t>
         </is>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3349,7 +3346,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3373,12 +3370,12 @@
           <t>198–153</t>
         </is>
       </c>
-      <c r="G23" s="18" t="n">
+      <c r="G23" s="17" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3402,12 +3399,12 @@
           <t>199–182</t>
         </is>
       </c>
-      <c r="G24" s="18" t="n">
+      <c r="G24" s="17" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3431,12 +3428,12 @@
           <t>166–165</t>
         </is>
       </c>
-      <c r="G25" s="18" t="n">
+      <c r="G25" s="17" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3460,7 +3457,7 @@
           <t>143–206</t>
         </is>
       </c>
-      <c r="G26" s="18" t="n">
+      <c r="G26" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3534,7 +3531,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
@@ -3561,7 +3558,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
@@ -3588,12 +3585,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Nestor Basket Marsciano  ✈️ FUORI REGIONE</t>
         </is>
@@ -3615,12 +3612,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Tissi Ittiri  ✈️ FUORI REGIONE</t>
         </is>
@@ -3649,7 +3646,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
@@ -3676,7 +3673,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
@@ -3703,12 +3700,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Codigoro Basket La Fenice  ✈️ FUORI REGIONE</t>
         </is>
@@ -3730,7 +3727,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
@@ -3764,7 +3761,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
@@ -3791,12 +3788,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Basket Loano  ✈️ FUORI REGIONE</t>
         </is>
@@ -3818,7 +3815,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
@@ -3845,7 +3842,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>E4</t>
         </is>
@@ -3879,7 +3876,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -3906,12 +3903,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>F2</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>San Francesco Ittiri  ✈️ FUORI REGIONE</t>
         </is>
@@ -3933,7 +3930,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
@@ -3960,7 +3957,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
@@ -4054,22 +4051,22 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Piazza Sandro Pertini · Monsummano Terme</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>Palazzetto principale. Entrambe le finalissime (U13 ore 13, U14 ore 15) + cerimonie apertura (ven 15:00) e chiusura (dom 17:00).</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
@@ -4096,7 +4093,7 @@
           <t>Palestra Comunale.</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
@@ -4123,7 +4120,7 @@
           <t>Palestra del Liceo Scientifico Coluccio Salutati.</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
@@ -4135,76 +4132,76 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Geodetica</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Piazza Sandro Pertini · Monsummano Terme</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Struttura adiacente al PalaCardelli, stessa piazza.</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>🍽</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Pool Bar</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Piazza Sandro Pertini · Monsummano Terme</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Punto di ristoro ufficiale per i pranzi. Stessa piazza del PalaCardelli.</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>☕</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Caffè Micky</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Cintolese · Monsummano Terme</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Punto di ristoro ufficiale per i pranzi delle squadre che giocano alla Pal. Cintolese.</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>📍 Apri su Maps</t>
         </is>
@@ -4276,17 +4273,17 @@
           <t>🎉 CERIMONIA DI APERTURA</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Ven 1 Maggio</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>15:00 – 15:45</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
@@ -4298,17 +4295,17 @@
           <t>🏆 CERIMONIA DI CHIUSURA</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Dom 3 Maggio</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>17:00 – 17:45</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>🏟 PalaCardelli</t>
         </is>
@@ -4380,7 +4377,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  ☕ Caffè Micky · 12:30 · 33 coperti</t>
         </is>
@@ -4425,7 +4422,7 @@
       <c r="E7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 42 coperti · ⚠ allergie</t>
         </is>
@@ -4448,7 +4445,7 @@
           <t>15 pax</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
         </is>
@@ -4474,7 +4471,7 @@
       <c r="E10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  ☕ Caffè Micky · 14:00 · 40 coperti · ⚠ allergie</t>
         </is>
@@ -4497,7 +4494,7 @@
           <t>24 pax</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
         </is>
@@ -4523,7 +4520,7 @@
       <c r="E13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  🍽 Pool Bar · 14:00 · 121 coperti · ⚠ allergie</t>
         </is>
@@ -4546,7 +4543,7 @@
           <t>36 pax</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco</t>
         </is>
@@ -4588,7 +4585,7 @@
           <t>18 pax</t>
         </is>
       </c>
-      <c r="E17" s="33" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco</t>
         </is>
@@ -4659,7 +4656,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  ☕ Caffè Micky · 12:30 · 16 coperti</t>
         </is>
@@ -4685,7 +4682,7 @@
       <c r="E24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  🍽 Pool Bar · 12:30 · 35 coperti</t>
         </is>
@@ -4711,7 +4708,7 @@
       <c r="E26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  ☕ Caffè Micky · 13:30 · 35 coperti · ⚠ allergie</t>
         </is>
@@ -4734,7 +4731,7 @@
           <t>4 pax</t>
         </is>
       </c>
-      <c r="E28" s="33" t="inlineStr">
+      <c r="E28" s="32" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco</t>
         </is>
@@ -4760,7 +4757,7 @@
       <c r="E29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  🍽 Pool Bar · 13:30 · 69 coperti · ⚠ allergie</t>
         </is>
@@ -4783,7 +4780,7 @@
           <t>24 pax</t>
         </is>
       </c>
-      <c r="E31" s="33" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>⚠ allergia peperoncino · intolleranza lattosio · allergia tonno</t>
         </is>
@@ -4806,7 +4803,7 @@
           <t>18 pax</t>
         </is>
       </c>
-      <c r="E32" s="33" t="inlineStr">
+      <c r="E32" s="32" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco</t>
         </is>
@@ -4829,7 +4826,7 @@
           <t>15 pax</t>
         </is>
       </c>
-      <c r="E33" s="33" t="inlineStr">
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>⚠ 1 celiaco · 1 intollerante lattosio</t>
         </is>
